--- a/Stock_OneClick/history/scan_result_20260601_172642.xlsx
+++ b/Stock_OneClick/history/scan_result_20260601_172642.xlsx
@@ -834,7 +834,7 @@
       <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>D0=294.07; 最新=2026-06-01; 相对D0=-9.65%; 本次触发=2026-05-22(第一买入点), 2026-05-29(正式买入); 历史重复1次; 重复日期=2026-05-29</t>
+          <t>D0=294.07; 最新=2026-06-01; 相对D0=-9.65%; 本次触发=2026-05-22(第一观察点), 2026-05-29(正式买入); 历史重复1次; 重复日期=2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-06-01(正式买入 | 第一买入点 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-01</t>
+          <t>D0=179.36; 最新=2026-06-01; 相对D0=5.37%; 本次触发=2026-05-22(预警买入), 2026-05-28(正式买入 | 预警买入), 2026-06-01(正式买入 | 第一观察点 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 本次触发=2026-05-22(正式买入), 2026-05-26(第一买入点); 历史重复1次; 重复日期=2026-05-26</t>
+          <t>D0=22.51; 最新=2026-06-01; 相对D0=3.64%; 本次触发=2026-05-22(正式买入), 2026-05-26(第一观察点); 历史重复1次; 重复日期=2026-05-26</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>D0=26.73; 最新=2026-06-01; 相对D0=11.11%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=26.73; 最新=2026-06-01; 相对D0=11.11%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>D0=137.65; 最新=2026-06-01; 相对D0=-5.94%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=137.65; 最新=2026-06-01; 相对D0=-5.94%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 第一买入点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
+          <t>D0=85.42; 最新=2026-06-01; 相对D0=35.74%; 本次触发=2026-05-22(正式买入 | 预警买入), 2026-05-27(正式买入 | 第一观察点 | 预警买入); 历史重复1次; 重复日期=2026-05-27</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>D0=156.27; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-22(第一买入点)</t>
+          <t>D0=156.27; 最新=2026-06-01; 相对D0=-0.97%; 本次触发=2026-05-22(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=22.62; 最新=2026-06-01; 相对D0=3.14%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-05-26(第一买入点), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
+          <t>D0=68.70; 最新=2026-06-01; 相对D0=-2.63%; 本次触发=2026-05-26(第一观察点), 2026-06-01(预警买入); 历史重复1次; 重复日期=2026-06-01</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%; 本次触发=2026-05-26(第一买入点)</t>
+          <t>D0=12.22; 最新=2026-06-01; 相对D0=5.48%; 本次触发=2026-05-26(第一观察点)</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>D0=15.98; 最新=2026-06-01; 相对D0=16.27%; 本次触发=2026-05-26(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=15.98; 最新=2026-06-01; 相对D0=16.27%; 本次触发=2026-05-26(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>D0=25.20; 最新=2026-06-01; 相对D0=10.16%; 本次触发=2026-05-27(正式买入 | 第一买入点)</t>
+          <t>D0=25.20; 最新=2026-06-01; 相对D0=10.16%; 本次触发=2026-05-27(正式买入 | 第一观察点)</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       <c r="P66" s="5" t="n"/>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%; 本次触发=2026-05-27(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=89.07; 最新=2026-06-01; 相对D0=30.18%; 本次触发=2026-05-27(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%; 本次触发=2026-05-29(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=259.21; 最新=2026-06-01; 相对D0=5.72%; 本次触发=2026-05-29(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       <c r="P109" s="5" t="n"/>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=189.00; 最新=2026-06-01; 相对D0=0.00%; 本次触发=2026-06-01(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -7006,6 +7006,7 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -7095,6 +7096,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="129"/>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
@@ -8731,6 +8733,7 @@
         </is>
       </c>
     </row>
+    <row r="160"/>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
@@ -9054,7 +9057,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -9102,7 +9105,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -10053,7 +10056,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -11076,7 +11079,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -11133,7 +11136,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -11241,7 +11244,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -13250,7 +13253,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -13368,7 +13371,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -13687,7 +13690,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
@@ -13747,7 +13750,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -14642,7 +14645,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -16211,7 +16214,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -16301,7 +16304,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -17711,7 +17714,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -20087,7 +20090,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20441,7 +20444,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -21155,7 +21158,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -21335,7 +21338,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23543,7 +23546,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -25130,7 +25133,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -28589,7 +28592,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -34406,7 +34409,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -38508,7 +38511,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -39785,7 +39788,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
